--- a/data/trans_orig/IP07C12-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07C12-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse que sus padres hayan tenido suficiente tiempo par él/ella en 2007 (tasa de respuesta: 89,59%)</t>
+          <t>Menores según la frecuencia de sentir que sus padres han tenido suficiente tiempo para él/ella en 2007 (tasa de respuesta: 89,59%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17410</t>
+          <t>17753</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29708</t>
+          <t>29469</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26665</t>
+          <t>26131</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39417</t>
+          <t>39312</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47102</t>
+          <t>46542</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65219</t>
+          <t>64600</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>51,49%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19564</t>
+          <t>19123</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31906</t>
+          <t>31050</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18682</t>
+          <t>18594</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31241</t>
+          <t>31281</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42301</t>
+          <t>41505</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60321</t>
+          <t>59154</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>47,15%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4480</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13561</t>
+          <t>13157</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>6678</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16078</t>
+          <t>15915</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13429</t>
+          <t>12839</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>26037</t>
+          <t>25928</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3620</t>
+          <t>3184</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42329</t>
+          <t>41210</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58858</t>
+          <t>57070</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42128</t>
+          <t>42100</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57693</t>
+          <t>56882</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>88528</t>
+          <t>88690</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>110370</t>
+          <t>110510</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>58,39%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26568</t>
+          <t>26940</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41198</t>
+          <t>41412</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21107</t>
+          <t>21349</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35276</t>
+          <t>35401</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>50265</t>
+          <t>51551</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>70712</t>
+          <t>71827</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,95%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8256</t>
+          <t>8253</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19179</t>
+          <t>19187</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8558</t>
+          <t>8497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>19596</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19174</t>
+          <t>19177</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>35230</t>
+          <t>34047</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3979</t>
+          <t>3959</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>3473</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25870</t>
+          <t>26520</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37395</t>
+          <t>37447</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32166</t>
+          <t>32268</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44150</t>
+          <t>44362</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61824</t>
+          <t>61683</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>77345</t>
+          <t>78346</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>66,94%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9975</t>
+          <t>10400</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20300</t>
+          <t>20482</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10183</t>
+          <t>10385</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21252</t>
+          <t>21675</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23727</t>
+          <t>23550</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37432</t>
+          <t>39187</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>33,48%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12831</t>
+          <t>13107</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11852</t>
+          <t>11498</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>10121</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>21744</t>
+          <t>21598</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3657</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>3604</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35735</t>
+          <t>36519</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50623</t>
+          <t>51033</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38483</t>
+          <t>38763</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54432</t>
+          <t>53756</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>79455</t>
+          <t>78704</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>99920</t>
+          <t>99841</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>59,99%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18954</t>
+          <t>19197</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>32512</t>
+          <t>32476</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22904</t>
+          <t>23185</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>37160</t>
+          <t>38071</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>45923</t>
+          <t>44772</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>65735</t>
+          <t>65512</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,36%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2372</t>
+          <t>2365</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>10005</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6716</t>
+          <t>6769</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16906</t>
+          <t>17179</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10367</t>
+          <t>10292</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>24215</t>
+          <t>23345</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2146</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>9633</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10164</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>135123</t>
+          <t>135102</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>161467</t>
+          <t>162667</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>153625</t>
+          <t>153294</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>181696</t>
+          <t>180354</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>295884</t>
+          <t>296265</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>335569</t>
+          <t>334936</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>55,99%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>85801</t>
+          <t>85757</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>111881</t>
+          <t>112550</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>85040</t>
+          <t>85103</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>111845</t>
+          <t>111615</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,47 +3623,47 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
+          <t>36,13%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>196888</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>178597</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>216615</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>32,91%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>29,86%</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
           <t>36,21%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>196888</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>179401</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>215682</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>32,91%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>29,99%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>36,05%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>26140</t>
+          <t>25806</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>44441</t>
+          <t>44105</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>33025</t>
+          <t>32011</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>51994</t>
+          <t>52021</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>64606</t>
+          <t>64283</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>90454</t>
+          <t>89667</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2794</t>
+          <t>2914</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>11074</t>
+          <t>11223</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>4602</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>12677</t>
+          <t>12879</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4943</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3338</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>642</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5377</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse que sus padres hayan tenido suficiente tiempo par él/ella en 2012 (tasa de respuesta: 95,62%)</t>
+          <t>Menores según la frecuencia de sentir que sus padres han tenido suficiente tiempo para él/ella en 2012 (tasa de respuesta: 95,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34242</t>
+          <t>34312</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46867</t>
+          <t>46697</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31534</t>
+          <t>31747</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46444</t>
+          <t>45626</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70873</t>
+          <t>69795</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89711</t>
+          <t>88689</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>65,94%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8466</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19295</t>
+          <t>20308</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20669</t>
+          <t>20939</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34547</t>
+          <t>35344</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32040</t>
+          <t>32879</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49671</t>
+          <t>50959</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,89%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>4145</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13398</t>
+          <t>12542</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10168</t>
+          <t>10292</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7595</t>
+          <t>7802</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19481</t>
+          <t>19618</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4598</t>
+          <t>4066</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47474</t>
+          <t>47620</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62788</t>
+          <t>62808</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43416</t>
+          <t>43621</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59236</t>
+          <t>58986</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96732</t>
+          <t>95456</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117997</t>
+          <t>117921</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>61,1%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23966</t>
+          <t>23403</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38065</t>
+          <t>37595</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26731</t>
+          <t>27120</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42329</t>
+          <t>42322</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>55042</t>
+          <t>53866</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>75003</t>
+          <t>75132</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,93%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5896</t>
+          <t>6468</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15813</t>
+          <t>16368</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5813</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15048</t>
+          <t>15108</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13855</t>
+          <t>13715</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27394</t>
+          <t>26705</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>4621</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5240</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32334</t>
+          <t>31635</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44719</t>
+          <t>44568</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39744</t>
+          <t>40752</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52144</t>
+          <t>52373</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>75977</t>
+          <t>74844</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>93429</t>
+          <t>93871</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,92%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13371</t>
+          <t>13375</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24937</t>
+          <t>24910</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11700</t>
+          <t>11486</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22891</t>
+          <t>22763</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27670</t>
+          <t>27375</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43558</t>
+          <t>43639</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,51%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>4342</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13084</t>
+          <t>13605</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8165</t>
+          <t>8113</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7813</t>
+          <t>7714</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18644</t>
+          <t>17664</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -6112,47 +6112,47 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4696</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1643</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>424</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>4682</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>6,78%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1643</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>425</t>
-        </is>
-      </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30649</t>
+          <t>30581</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46803</t>
+          <t>46679</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37612</t>
+          <t>37420</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53749</t>
+          <t>53359</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>73144</t>
+          <t>73563</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>95671</t>
+          <t>95695</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,5%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26720</t>
+          <t>25589</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>41608</t>
+          <t>40785</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22912</t>
+          <t>23235</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>37884</t>
+          <t>38325</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>53860</t>
+          <t>52696</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>75983</t>
+          <t>74914</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>42,67%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6612</t>
+          <t>6908</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17836</t>
+          <t>18330</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7676</t>
+          <t>7882</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19387</t>
+          <t>19226</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>17330</t>
+          <t>16770</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>33465</t>
+          <t>33151</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>5643</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5504</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>811</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7175</t>
+          <t>7779</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>159390</t>
+          <t>159205</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>188044</t>
+          <t>187305</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>168737</t>
+          <t>167659</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>197669</t>
+          <t>197700</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>335458</t>
+          <t>335088</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>375621</t>
+          <t>375950</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>58,99%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>83211</t>
+          <t>83959</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>111135</t>
+          <t>110781</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>95524</t>
+          <t>95968</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>122069</t>
+          <t>122949</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,47 +7265,47 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
+          <t>29,43%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>37,71%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>205119</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>186679</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>225558</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>32,18%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>29,29%</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>37,44%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>205119</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>185450</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>224222</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>32,18%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>29,1%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,39%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>28234</t>
+          <t>28396</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>47554</t>
+          <t>47528</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>23949</t>
+          <t>23293</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>41998</t>
+          <t>41613</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>57307</t>
+          <t>56242</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>83439</t>
+          <t>81717</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>922</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9084</t>
+          <t>8894</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>3707</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>12805</t>
+          <t>13275</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse que sus padres hayan tenido suficiente tiempo par él/ella en 2016 (tasa de respuesta: 95,18%)</t>
+          <t>Menores según la frecuencia de sentir que sus padres han tenido suficiente tiempo para él/ella en 2016 (tasa de respuesta: 95,18%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30590</t>
+          <t>29461</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44163</t>
+          <t>43850</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36300</t>
+          <t>36624</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50566</t>
+          <t>50616</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70903</t>
+          <t>71023</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>91759</t>
+          <t>91182</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,11%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17788</t>
+          <t>18043</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31131</t>
+          <t>32522</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16634</t>
+          <t>16644</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29594</t>
+          <t>30028</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37895</t>
+          <t>37654</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56618</t>
+          <t>56863</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,6%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>3021</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11690</t>
+          <t>11580</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8685</t>
+          <t>8849</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17391</t>
+          <t>17474</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4737</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4492</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40763</t>
+          <t>41069</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57502</t>
+          <t>56484</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42126</t>
+          <t>41855</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58875</t>
+          <t>58142</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>87460</t>
+          <t>86951</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>110633</t>
+          <t>111578</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,61%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33546</t>
+          <t>34513</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50469</t>
+          <t>49799</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32040</t>
+          <t>32772</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48803</t>
+          <t>49675</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>72434</t>
+          <t>71618</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>95192</t>
+          <t>95323</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,65%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4189</t>
+          <t>4227</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13317</t>
+          <t>13307</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5504</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15255</t>
+          <t>15316</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12407</t>
+          <t>12352</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>25715</t>
+          <t>24752</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,11%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>572</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6190</t>
+          <t>6043</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7655</t>
+          <t>7713</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3453</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36545</t>
+          <t>36949</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50021</t>
+          <t>49640</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35091</t>
+          <t>35569</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49344</t>
+          <t>49477</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>76620</t>
+          <t>76084</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>95740</t>
+          <t>95647</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,18%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11755</t>
+          <t>11559</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23241</t>
+          <t>23137</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18487</t>
+          <t>18631</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32274</t>
+          <t>32007</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34424</t>
+          <t>33445</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51459</t>
+          <t>52637</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>36,42%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3615</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12494</t>
+          <t>12749</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2629</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10770</t>
+          <t>10167</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8221</t>
+          <t>8225</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20137</t>
+          <t>19302</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4338</t>
+          <t>5374</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6065</t>
+          <t>6473</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -9837,7 +9837,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4572</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4817</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>44449</t>
+          <t>44883</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>61737</t>
+          <t>62435</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41758</t>
+          <t>42800</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>59371</t>
+          <t>59244</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>91995</t>
+          <t>92632</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>117734</t>
+          <t>117399</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,18%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23992</t>
+          <t>24190</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>39659</t>
+          <t>40766</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>26571</t>
+          <t>27071</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42682</t>
+          <t>42567</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>55301</t>
+          <t>54913</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>78457</t>
+          <t>77085</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,2%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>11095</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22674</t>
+          <t>22977</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>7887</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19086</t>
+          <t>19299</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>20619</t>
+          <t>20761</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>37659</t>
+          <t>37703</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5372</t>
+          <t>5689</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>4224</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>714</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6212</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>167410</t>
+          <t>167370</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>198310</t>
+          <t>197316</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>170115</t>
+          <t>172859</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>204679</t>
+          <t>203809</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>347809</t>
+          <t>349969</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>392516</t>
+          <t>393692</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>57,0%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>99899</t>
+          <t>101754</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>129428</t>
+          <t>131135</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>107432</t>
+          <t>107317</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>138193</t>
+          <t>137237</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>217401</t>
+          <t>217072</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>259018</t>
+          <t>259367</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,55%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>28568</t>
+          <t>28455</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>48037</t>
+          <t>48060</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>24330</t>
+          <t>24820</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>42482</t>
+          <t>42412</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>56949</t>
+          <t>58028</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>83184</t>
+          <t>84058</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2904</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>11262</t>
+          <t>11489</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>705</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>7801</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5268</t>
+          <t>5066</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>15465</t>
+          <t>15192</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -11196,54 +11196,54 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>5545</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>5449</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>570</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
